--- a/public/reading-template.xlsx
+++ b/public/reading-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaquibfaridi/Desktop/Aaquib/cpcompliance/frontend/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BDBBEB-9866-8241-9DB7-32D643A3E9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C064031-C864-9942-B8B1-240C6E24A849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
@@ -36,12 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Reading Date (DD/MM/YYYY)</t>
   </si>
   <si>
     <t>Reading (kWh)</t>
+  </si>
+  <si>
+    <t>Reference</t>
   </si>
 </sst>
 </file>
@@ -77,16 +80,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -104,11 +121,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:B1048576" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:B1048576" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (DD/MM/YYYY)"/>
-    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="Reading (kWh)"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:C1048574" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:C1048574" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
+  <tableColumns count="3">
+    <tableColumn id="3" xr3:uid="{F0377C27-1EE1-4644-AAD0-066046ED73E1}" name="Reference"/>
+    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (DD/MM/YYYY)" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="Reading (kWh)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -431,18 +449,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C961255-8D4E-8445-9D9B-F5A2E3A7180D}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="46.1640625" customWidth="1"/>
+    <col min="2" max="2" width="40" style="3" customWidth="1"/>
+    <col min="3" max="3" width="46.1640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
     </row>

--- a/public/reading-template.xlsx
+++ b/public/reading-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaquibfaridi/Desktop/Aaquib/cpcompliance/frontend/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C064031-C864-9942-B8B1-240C6E24A849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5662FF78-908E-3540-A2A0-3AFB6C44C9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
@@ -38,13 +38,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Reading Date (DD/MM/YYYY)</t>
-  </si>
-  <si>
     <t>Reading (kWh)</t>
   </si>
   <si>
     <t>Reference</t>
+  </si>
+  <si>
+    <t>Reading Date (YYYY/MM/DD)</t>
   </si>
 </sst>
 </file>
@@ -85,14 +85,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -102,7 +102,7 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -125,7 +125,7 @@
   <autoFilter ref="A1:C1048574" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
   <tableColumns count="3">
     <tableColumn id="3" xr3:uid="{F0377C27-1EE1-4644-AAD0-066046ED73E1}" name="Reference"/>
-    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (DD/MM/YYYY)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (YYYY/MM/DD)" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="Reading (kWh)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -453,19 +453,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="40" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.1640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="40" style="5" customWidth="1"/>
+    <col min="3" max="3" width="46.1640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/public/reading-template.xlsx
+++ b/public/reading-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaquibfaridi/Desktop/Aaquib/cpcompliance/frontend/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaquibfaridi\Downloads\tdk\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5662FF78-908E-3540-A2A0-3AFB6C44C9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C24157-8B1A-4DAA-8014-090202167664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
+    <workbookView xWindow="3490" yWindow="2720" windowWidth="15710" windowHeight="7360" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,10 +41,10 @@
     <t>Reading (kWh)</t>
   </si>
   <si>
-    <t>Reference</t>
+    <t>Reading Date (DD/MM/YYYY)</t>
   </si>
   <si>
-    <t>Reading Date (YYYY/MM/DD)</t>
+    <t>Meter Reference</t>
   </si>
 </sst>
 </file>
@@ -124,8 +124,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:C1048574" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:C1048574" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
   <tableColumns count="3">
-    <tableColumn id="3" xr3:uid="{F0377C27-1EE1-4644-AAD0-066046ED73E1}" name="Reference"/>
-    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (YYYY/MM/DD)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{F0377C27-1EE1-4644-AAD0-066046ED73E1}" name="Meter Reference"/>
+    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (DD/MM/YYYY)" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="Reading (kWh)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -450,19 +450,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C961255-8D4E-8445-9D9B-F5A2E3A7180D}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="40" style="5" customWidth="1"/>
     <col min="3" max="3" width="46.1640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>

--- a/public/reading-template.xlsx
+++ b/public/reading-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaquibfaridi\Downloads\tdk\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C24157-8B1A-4DAA-8014-090202167664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DA2A5F-BDF5-4008-9120-984290A433A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3490" yWindow="2720" windowWidth="15710" windowHeight="7360" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B632CFA-6A58-9A49-9EAD-C6A770500F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Reading (kWh)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Reading Date (DD/MM/YYYY)</t>
   </si>
   <si>
     <t>Meter Reference</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Reading Unit</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>KwH</t>
+  </si>
+  <si>
+    <t>ltrs</t>
+  </si>
+  <si>
+    <t>units</t>
   </si>
 </sst>
 </file>
@@ -68,7 +83,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -76,11 +91,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -93,11 +117,92 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -121,14 +226,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:C1048574" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:C1048574" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}" name="Table2" displayName="Table2" ref="A1:D1048574" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:D1048574" xr:uid="{B032FA8C-8501-D149-99E4-B64930D6396E}"/>
+  <tableColumns count="4">
     <tableColumn id="3" xr3:uid="{F0377C27-1EE1-4644-AAD0-066046ED73E1}" name="Meter Reference"/>
-    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (DD/MM/YYYY)" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="Reading (kWh)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{99664C71-59F8-9441-8ADD-387DD38F7D48}" name="Reading Date (DD/MM/YYYY)" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{6021C340-84A2-4092-89AF-2D3CC7A47B99}" name="Reading" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{6F160CE5-9BF6-2A40-BF8D-DA6CC5EF89C8}" name="Reading Unit" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F4C33F12-E26A-4EE7-A49C-2FD854E61E3F}" name="Table4" displayName="Table4" ref="H2:H5" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="3">
+  <autoFilter ref="H2:H5" xr:uid="{F4C33F12-E26A-4EE7-A49C-2FD854E61E3F}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{2925C465-93BD-4CCC-987F-E578B5FB58EC}" name="units" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -449,29 +565,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C961255-8D4E-8445-9D9B-F5A2E3A7180D}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="40" style="5" customWidth="1"/>
-    <col min="3" max="3" width="46.1640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="30.25" customWidth="1"/>
+    <col min="2" max="3" width="31.4140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H4" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H5" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{18EE716D-3831-4418-A34E-4DD1F0A0457B}">
+      <formula1>$H$3:$H$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>